--- a/Std-plan ab z17.xlsx
+++ b/Std-plan ab z17.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4cfeafcae5aef467/visual studios/z17/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23F43EF4-D25E-42E3-8E0D-8BC730A41C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{23F43EF4-D25E-42E3-8E0D-8BC730A41C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61264D8A-31A6-482C-9F89-1FF5467D856F}"/>
   <bookViews>
-    <workbookView xWindow="14040" yWindow="11580" windowWidth="30960" windowHeight="18810" tabRatio="926" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18135" yWindow="9810" windowWidth="30960" windowHeight="18810" tabRatio="926" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UV" sheetId="1" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18088" uniqueCount="2378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18089" uniqueCount="2379">
   <si>
     <t>Zeitlimitsekunden für solver</t>
   </si>
@@ -7259,6 +7259,9 @@
   </si>
   <si>
     <t>Hohlmax Woche hart</t>
+  </si>
+  <si>
+    <t>nur bei Überschreitung der oberen Grenze</t>
   </si>
 </sst>
 </file>
@@ -77384,13 +77387,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A371:H371"/>
-    <mergeCell ref="A182:H182"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A5:H5"/>
     <mergeCell ref="A548:H548"/>
     <mergeCell ref="A359:H359"/>
     <mergeCell ref="A186:H186"/>
@@ -77401,6 +77397,13 @@
     <mergeCell ref="A540:H540"/>
     <mergeCell ref="A536:H536"/>
     <mergeCell ref="A194:H194"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A371:H371"/>
+    <mergeCell ref="A182:H182"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
@@ -79297,12 +79300,15 @@
       <c r="A17"/>
       <c r="B17" s="38"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="38" t="s">
         <v>3</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>2378</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
